--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2020_la_araucania.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2020_la_araucania.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:38</t>
+    <t xml:space="preserve">2026-10-05 01:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>794351.12</v>
+        <v>794351.13</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>976086</v>
@@ -601,10 +601,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>947146.12</v>
+        <v>947146.13</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
@@ -634,7 +634,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1057308.12</v>
+        <v>1057308.13</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>1298591</v>
